--- a/EXP/400_50_Unet_smooth0.001/results/train/train_result.xlsx
+++ b/EXP/400_50_Unet_smooth0.001/results/train/train_result.xlsx
@@ -450,13 +450,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.38595</v>
+        <v>1.39206</v>
       </c>
       <c r="C2" t="n">
-        <v>0.36424</v>
+        <v>0.34197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.49095</v>
+        <v>0.46813</v>
       </c>
     </row>
     <row r="3">
@@ -464,13 +464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25117</v>
+        <v>1.26791</v>
       </c>
       <c r="C3" t="n">
-        <v>0.47307</v>
+        <v>0.44661</v>
       </c>
       <c r="D3" t="n">
-        <v>0.59811</v>
+        <v>0.5732</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.19519</v>
+        <v>1.21703</v>
       </c>
       <c r="C4" t="n">
-        <v>0.58213</v>
+        <v>0.52028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.69884</v>
+        <v>0.64193</v>
       </c>
     </row>
     <row r="5">
@@ -492,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.15092</v>
+        <v>1.17014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.62683</v>
+        <v>0.58718</v>
       </c>
       <c r="D5" t="n">
-        <v>0.73932</v>
+        <v>0.7037099999999999</v>
       </c>
     </row>
     <row r="6">
@@ -506,13 +506,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.10739</v>
+        <v>1.12861</v>
       </c>
       <c r="C6" t="n">
-        <v>0.65611</v>
+        <v>0.63185</v>
       </c>
       <c r="D6" t="n">
-        <v>0.76534</v>
+        <v>0.74399</v>
       </c>
     </row>
     <row r="7">
@@ -520,13 +520,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.0656</v>
+        <v>1.08731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.67522</v>
+        <v>0.66482</v>
       </c>
       <c r="D7" t="n">
-        <v>0.78186</v>
+        <v>0.77303</v>
       </c>
     </row>
     <row r="8">
@@ -534,13 +534,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.02202</v>
+        <v>1.05427</v>
       </c>
       <c r="C8" t="n">
-        <v>0.69701</v>
+        <v>0.67884</v>
       </c>
       <c r="D8" t="n">
-        <v>0.80014</v>
+        <v>0.78492</v>
       </c>
     </row>
     <row r="9">
@@ -548,13 +548,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.98293</v>
+        <v>1.0142</v>
       </c>
       <c r="C9" t="n">
-        <v>0.71064</v>
+        <v>0.70159</v>
       </c>
       <c r="D9" t="n">
-        <v>0.81142</v>
+        <v>0.80404</v>
       </c>
     </row>
     <row r="10">
@@ -562,13 +562,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.94069</v>
+        <v>0.98029</v>
       </c>
       <c r="C10" t="n">
-        <v>0.72781</v>
+        <v>0.71302</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8253200000000001</v>
+        <v>0.81341</v>
       </c>
     </row>
     <row r="11">
@@ -576,13 +576,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.90388</v>
+        <v>0.93809</v>
       </c>
       <c r="C11" t="n">
-        <v>0.73982</v>
+        <v>0.73463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83478</v>
+        <v>0.83075</v>
       </c>
     </row>
     <row r="12">
@@ -590,13 +590,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.86497</v>
+        <v>0.90595</v>
       </c>
       <c r="C12" t="n">
-        <v>0.75386</v>
+        <v>0.74192</v>
       </c>
       <c r="D12" t="n">
-        <v>0.84565</v>
+        <v>0.83644</v>
       </c>
     </row>
     <row r="13">
@@ -604,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.82989</v>
+        <v>0.87435</v>
       </c>
       <c r="C13" t="n">
-        <v>0.76512</v>
+        <v>0.75065</v>
       </c>
       <c r="D13" t="n">
-        <v>0.85422</v>
+        <v>0.84322</v>
       </c>
     </row>
     <row r="14">
@@ -618,13 +618,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.79758</v>
+        <v>0.84297</v>
       </c>
       <c r="C14" t="n">
-        <v>0.77399</v>
+        <v>0.76005</v>
       </c>
       <c r="D14" t="n">
-        <v>0.86089</v>
+        <v>0.85041</v>
       </c>
     </row>
     <row r="15">
@@ -632,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.81626</v>
       </c>
       <c r="C15" t="n">
-        <v>0.78225</v>
+        <v>0.76598</v>
       </c>
       <c r="D15" t="n">
-        <v>0.86697</v>
+        <v>0.85489</v>
       </c>
     </row>
     <row r="16">
@@ -646,13 +646,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.73953</v>
+        <v>0.78859</v>
       </c>
       <c r="C16" t="n">
-        <v>0.79169</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.87385</v>
+        <v>0.86064</v>
       </c>
     </row>
     <row r="17">
@@ -660,13 +660,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7138</v>
+        <v>0.7573</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79978</v>
+        <v>0.78577</v>
       </c>
       <c r="D17" t="n">
-        <v>0.87964</v>
+        <v>0.86956</v>
       </c>
     </row>
     <row r="18">
@@ -674,13 +674,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.69092</v>
+        <v>0.73606</v>
       </c>
       <c r="C18" t="n">
-        <v>0.80702</v>
+        <v>0.7906300000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8847699999999999</v>
+        <v>0.87308</v>
       </c>
     </row>
     <row r="19">
@@ -688,13 +688,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.67503</v>
+        <v>0.73898</v>
       </c>
       <c r="C19" t="n">
-        <v>0.80932</v>
+        <v>0.77638</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8863799999999999</v>
+        <v>0.86246</v>
       </c>
     </row>
     <row r="20">
@@ -702,13 +702,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.65808</v>
+        <v>0.69801</v>
       </c>
       <c r="C20" t="n">
-        <v>0.81387</v>
+        <v>0.79979</v>
       </c>
       <c r="D20" t="n">
-        <v>0.88955</v>
+        <v>0.87966</v>
       </c>
     </row>
     <row r="21">
@@ -716,13 +716,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.63857</v>
+        <v>0.67567</v>
       </c>
       <c r="C21" t="n">
-        <v>0.82181</v>
+        <v>0.80866</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89505</v>
+        <v>0.8859399999999999</v>
       </c>
     </row>
     <row r="22">
@@ -730,13 +730,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.63054</v>
+        <v>0.657</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8213200000000001</v>
+        <v>0.81548</v>
       </c>
       <c r="D22" t="n">
-        <v>0.89471</v>
+        <v>0.89071</v>
       </c>
     </row>
     <row r="23">
@@ -744,13 +744,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.607</v>
+        <v>0.65098</v>
       </c>
       <c r="C23" t="n">
-        <v>0.83355</v>
+        <v>0.81258</v>
       </c>
       <c r="D23" t="n">
-        <v>0.90305</v>
+        <v>0.88868</v>
       </c>
     </row>
     <row r="24">
@@ -758,13 +758,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.60237</v>
+        <v>0.63855</v>
       </c>
       <c r="C24" t="n">
-        <v>0.83196</v>
+        <v>0.81614</v>
       </c>
       <c r="D24" t="n">
-        <v>0.90197</v>
+        <v>0.89117</v>
       </c>
     </row>
     <row r="25">
@@ -772,13 +772,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5898</v>
+        <v>0.61813</v>
       </c>
       <c r="C25" t="n">
-        <v>0.83672</v>
+        <v>0.8264899999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9051900000000001</v>
+        <v>0.8982599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -786,13 +786,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.58322</v>
+        <v>0.61145</v>
       </c>
       <c r="C26" t="n">
-        <v>0.83813</v>
+        <v>0.82682</v>
       </c>
       <c r="D26" t="n">
-        <v>0.90613</v>
+        <v>0.8985</v>
       </c>
     </row>
     <row r="27">
@@ -800,13 +800,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.59023</v>
+        <v>0.61715</v>
       </c>
       <c r="C27" t="n">
-        <v>0.83012</v>
+        <v>0.81809</v>
       </c>
       <c r="D27" t="n">
-        <v>0.90068</v>
+        <v>0.89245</v>
       </c>
     </row>
     <row r="28">
@@ -814,13 +814,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.56419</v>
+        <v>0.59168</v>
       </c>
       <c r="C28" t="n">
-        <v>0.84589</v>
+        <v>0.83318</v>
       </c>
       <c r="D28" t="n">
-        <v>0.91127</v>
+        <v>0.90278</v>
       </c>
     </row>
     <row r="29">
@@ -828,13 +828,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.55783</v>
+        <v>0.58081</v>
       </c>
       <c r="C29" t="n">
-        <v>0.84789</v>
+        <v>0.83796</v>
       </c>
       <c r="D29" t="n">
-        <v>0.91261</v>
+        <v>0.90601</v>
       </c>
     </row>
     <row r="30">
@@ -842,13 +842,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5595599999999999</v>
+        <v>0.58533</v>
       </c>
       <c r="C30" t="n">
-        <v>0.84448</v>
+        <v>0.83184</v>
       </c>
       <c r="D30" t="n">
-        <v>0.91032</v>
+        <v>0.90188</v>
       </c>
     </row>
     <row r="31">
@@ -856,13 +856,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.54872</v>
+        <v>0.58766</v>
       </c>
       <c r="C31" t="n">
-        <v>0.84999</v>
+        <v>0.82743</v>
       </c>
       <c r="D31" t="n">
-        <v>0.91396</v>
+        <v>0.89879</v>
       </c>
     </row>
     <row r="32">
@@ -870,13 +870,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.54538</v>
+        <v>0.56243</v>
       </c>
       <c r="C32" t="n">
-        <v>0.85071</v>
+        <v>0.84358</v>
       </c>
       <c r="D32" t="n">
-        <v>0.91442</v>
+        <v>0.90974</v>
       </c>
     </row>
     <row r="33">
@@ -884,13 +884,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.54235</v>
+        <v>0.55528</v>
       </c>
       <c r="C33" t="n">
-        <v>0.85137</v>
+        <v>0.8464</v>
       </c>
       <c r="D33" t="n">
-        <v>0.91486</v>
+        <v>0.9116</v>
       </c>
     </row>
     <row r="34">
@@ -898,13 +898,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.53232</v>
+        <v>0.54998</v>
       </c>
       <c r="C34" t="n">
-        <v>0.85699</v>
+        <v>0.84854</v>
       </c>
       <c r="D34" t="n">
-        <v>0.91851</v>
+        <v>0.91303</v>
       </c>
     </row>
     <row r="35">
@@ -912,13 +912,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.53016</v>
+        <v>0.5450199999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.85725</v>
+        <v>0.85042</v>
       </c>
       <c r="D35" t="n">
-        <v>0.91869</v>
+        <v>0.9142400000000001</v>
       </c>
     </row>
     <row r="36">
@@ -926,13 +926,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.53855</v>
+        <v>0.54131</v>
       </c>
       <c r="C36" t="n">
-        <v>0.84987</v>
+        <v>0.85121</v>
       </c>
       <c r="D36" t="n">
-        <v>0.91387</v>
+        <v>0.91477</v>
       </c>
     </row>
     <row r="37">
@@ -940,13 +940,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.52042</v>
+        <v>0.54196</v>
       </c>
       <c r="C37" t="n">
-        <v>0.86189</v>
+        <v>0.8494</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9216800000000001</v>
+        <v>0.91359</v>
       </c>
     </row>
     <row r="38">
@@ -954,13 +954,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.51563</v>
+        <v>0.53855</v>
       </c>
       <c r="C38" t="n">
-        <v>0.86434</v>
+        <v>0.8507</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9232399999999999</v>
+        <v>0.91443</v>
       </c>
     </row>
     <row r="39">
@@ -968,13 +968,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.52177</v>
+        <v>0.52784</v>
       </c>
       <c r="C39" t="n">
-        <v>0.85906</v>
+        <v>0.85719</v>
       </c>
       <c r="D39" t="n">
-        <v>0.91986</v>
+        <v>0.91865</v>
       </c>
     </row>
     <row r="40">
@@ -982,13 +982,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.515</v>
+        <v>0.52756</v>
       </c>
       <c r="C40" t="n">
-        <v>0.86312</v>
+        <v>0.85598</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9224599999999999</v>
+        <v>0.91786</v>
       </c>
     </row>
     <row r="41">
@@ -996,13 +996,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5122</v>
+        <v>0.52702</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.85583</v>
       </c>
       <c r="D41" t="n">
-        <v>0.92328</v>
+        <v>0.91775</v>
       </c>
     </row>
     <row r="42">
@@ -1010,13 +1010,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.50753</v>
+        <v>0.52367</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8668</v>
+        <v>0.85726</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9248</v>
+        <v>0.9186800000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1024,13 +1024,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.50576</v>
+        <v>0.51725</v>
       </c>
       <c r="C43" t="n">
-        <v>0.86764</v>
+        <v>0.86073</v>
       </c>
       <c r="D43" t="n">
-        <v>0.92531</v>
+        <v>0.92093</v>
       </c>
     </row>
     <row r="44">
@@ -1038,13 +1038,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.50573</v>
+        <v>0.51555</v>
       </c>
       <c r="C44" t="n">
-        <v>0.86692</v>
+        <v>0.86137</v>
       </c>
       <c r="D44" t="n">
-        <v>0.92488</v>
+        <v>0.92134</v>
       </c>
     </row>
     <row r="45">
@@ -1052,13 +1052,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.50396</v>
+        <v>0.51197</v>
       </c>
       <c r="C45" t="n">
-        <v>0.86766</v>
+        <v>0.86325</v>
       </c>
       <c r="D45" t="n">
-        <v>0.92535</v>
+        <v>0.92253</v>
       </c>
     </row>
     <row r="46">
@@ -1066,13 +1066,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.49709</v>
+        <v>0.51451</v>
       </c>
       <c r="C46" t="n">
-        <v>0.87215</v>
+        <v>0.8609599999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9282</v>
+        <v>0.92105</v>
       </c>
     </row>
     <row r="47">
@@ -1080,13 +1080,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.4999</v>
+        <v>0.50335</v>
       </c>
       <c r="C47" t="n">
-        <v>0.86977</v>
+        <v>0.8682299999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.92665</v>
+        <v>0.92572</v>
       </c>
     </row>
     <row r="48">
@@ -1094,13 +1094,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.50273</v>
+        <v>0.5137</v>
       </c>
       <c r="C48" t="n">
-        <v>0.86715</v>
+        <v>0.86034</v>
       </c>
       <c r="D48" t="n">
-        <v>0.92503</v>
+        <v>0.92066</v>
       </c>
     </row>
     <row r="49">
@@ -1108,13 +1108,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.50307</v>
+        <v>0.51261</v>
       </c>
       <c r="C49" t="n">
-        <v>0.86676</v>
+        <v>0.8606200000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0.92476</v>
+        <v>0.92083</v>
       </c>
     </row>
     <row r="50">
@@ -1122,13 +1122,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.49231</v>
+        <v>0.50083</v>
       </c>
       <c r="C50" t="n">
-        <v>0.87383</v>
+        <v>0.86851</v>
       </c>
       <c r="D50" t="n">
-        <v>0.92923</v>
+        <v>0.92587</v>
       </c>
     </row>
     <row r="51">
@@ -1136,13 +1136,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.48999</v>
+        <v>0.49588</v>
       </c>
       <c r="C51" t="n">
-        <v>0.87497</v>
+        <v>0.87171</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9299500000000001</v>
+        <v>0.92791</v>
       </c>
     </row>
   </sheetData>
